--- a/data/analysis_results/overview_aae.xlsx
+++ b/data/analysis_results/overview_aae.xlsx
@@ -49,13 +49,13 @@
     <t>Mistral-7B-Instruct-v0.2</t>
   </si>
   <si>
+    <t>Qwen2.5-72B-Instruct</t>
+  </si>
+  <si>
     <t>phi-4</t>
   </si>
   <si>
     <t>Llama-3.3-70B-Instruct</t>
-  </si>
-  <si>
-    <t>Qwen2.5-72B-Instruct</t>
   </si>
   <si>
     <t>Qwen3-32B</t>
@@ -71,14 +71,14 @@
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>ASR: 0.20
+V1: 129 V2: 2 Vties: 11</t>
+  </si>
+  <si>
     <t>ASR: 0.57
 V1: 128 V2: 4 Vties: 3</t>
   </si>
   <si>
-    <t>ASR: 0.20
-V1: 129 V2: 2 Vties: 11</t>
-  </si>
-  <si>
     <t>ASR: 0.74
 V1: 136 V2: 3 Vties: 2</t>
   </si>
@@ -87,14 +87,14 @@
 V1: 41 V2: 10 Vties: 89</t>
   </si>
   <si>
+    <t>ASR: 0.81
+V1: 81 V2: 19 Vties: 42</t>
+  </si>
+  <si>
     <t>ASR: 0.78
 V1: 81 V2: 25 Vties: 7</t>
   </si>
   <si>
-    <t>ASR: 0.81
-V1: 81 V2: 19 Vties: 42</t>
-  </si>
-  <si>
     <t>ASR: 0.83
 V1: 95 V2: 34 Vties: 12</t>
   </si>
@@ -111,6 +111,10 @@
 V1: 39 V2: 21 Vties: 81</t>
   </si>
   <si>
+    <t>ASR: 0.41
+V1: 92 V2: 16 Vties: 34</t>
+  </si>
+  <si>
     <t>ASR: 0.77
 V1: 88 V2: 20 Vties: 12</t>
   </si>
@@ -119,14 +123,14 @@
 V1: 61 V2: 35 Vties: 46</t>
   </si>
   <si>
-    <t>ASR: 0.41
-V1: 92 V2: 16 Vties: 34</t>
-  </si>
-  <si>
     <t>ASR: 0.29
 V1: 90 V2: 1 Vties: 50</t>
   </si>
   <si>
+    <t>ASR: 0.30
+V1: 135 V2: 1 Vties: 6</t>
+  </si>
+  <si>
     <t>ASR: 0.22
 V1: 138 V2: 0 Vties: 4</t>
   </si>
@@ -135,10 +139,6 @@
 V1: 133 V2: 3 Vties: 6</t>
   </si>
   <si>
-    <t>ASR: 0.30
-V1: 135 V2: 1 Vties: 6</t>
-  </si>
-  <si>
     <t>ASR: 0.62
 V1: 34 V2: 15 Vties: 92</t>
   </si>
@@ -167,6 +167,10 @@
 V1: 36 V2: 7 Vties: 99</t>
   </si>
   <si>
+    <t>ASR: 0.95
+V1: 58 V2: 12 Vties: 72</t>
+  </si>
+  <si>
     <t>ASR: 0.98
 V1: 81 V2: 24 Vties: 11</t>
   </si>
@@ -175,10 +179,6 @@
 V1: 58 V2: 29 Vties: 55</t>
   </si>
   <si>
-    <t>ASR: 0.95
-V1: 58 V2: 12 Vties: 72</t>
-  </si>
-  <si>
     <t>ASR: 0.94
 V1: 86 V2: 35 Vties: 21</t>
   </si>
@@ -188,14 +188,14 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 129 V2: 2 Vties: 11</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 128 V2: 4 Vties: 3</t>
   </si>
   <si>
     <t>AASR: 0.00
-V1: 129 V2: 2 Vties: 11</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 136 V2: 3 Vties: 2</t>
   </si>
   <si>
@@ -204,11 +204,11 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 81 V2: 19 Vties: 42</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 81 V2: 25 Vties: 7</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 81 V2: 19 Vties: 42</t>
   </si>
   <si>
     <t>AASR: 0.00
@@ -228,6 +228,10 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 92 V2: 16 Vties: 34</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 88 V2: 20 Vties: 12</t>
   </si>
   <si>
@@ -236,14 +240,14 @@
   </si>
   <si>
     <t>AASR: 0.00
-V1: 92 V2: 16 Vties: 34</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 90 V2: 1 Vties: 50</t>
   </si>
   <si>
     <t>AASR: 0.00
+V1: 135 V2: 1 Vties: 6</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 138 V2: 0 Vties: 4</t>
   </si>
   <si>
@@ -252,10 +256,6 @@
   </si>
   <si>
     <t>AASR: 0.00
-V1: 135 V2: 1 Vties: 6</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 34 V2: 15 Vties: 92</t>
   </si>
   <si>
@@ -284,15 +284,15 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 58 V2: 12 Vties: 72</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 81 V2: 24 Vties: 11</t>
   </si>
   <si>
     <t>AASR: 0.00
 V1: 58 V2: 29 Vties: 55</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
     <t>AASR: 0.00
@@ -303,14 +303,14 @@
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>FR: 0.26
+V1: 129 V2: 2 Vties: 11</t>
+  </si>
+  <si>
     <t>FR: 0.56
 V1: 128 V2: 4 Vties: 3</t>
   </si>
   <si>
-    <t>FR: 0.26
-V1: 129 V2: 2 Vties: 11</t>
-  </si>
-  <si>
     <t>FR: 0.73
 V1: 136 V2: 3 Vties: 2</t>
   </si>
@@ -319,14 +319,14 @@
 V1: 41 V2: 10 Vties: 89</t>
   </si>
   <si>
+    <t>FR: 0.76
+V1: 81 V2: 19 Vties: 42</t>
+  </si>
+  <si>
     <t>FR: 0.62
 V1: 81 V2: 25 Vties: 7</t>
   </si>
   <si>
-    <t>FR: 0.76
-V1: 81 V2: 19 Vties: 42</t>
-  </si>
-  <si>
     <t>FR: 0.65
 V1: 95 V2: 34 Vties: 12</t>
   </si>
@@ -343,6 +343,10 @@
 V1: 39 V2: 21 Vties: 81</t>
   </si>
   <si>
+    <t>FR: 0.51
+V1: 92 V2: 16 Vties: 34</t>
+  </si>
+  <si>
     <t>FR: 0.67
 V1: 88 V2: 20 Vties: 12</t>
   </si>
@@ -351,14 +355,14 @@
 V1: 61 V2: 35 Vties: 46</t>
   </si>
   <si>
-    <t>FR: 0.51
-V1: 92 V2: 16 Vties: 34</t>
-  </si>
-  <si>
     <t>FR: 0.54
 V1: 90 V2: 1 Vties: 50</t>
   </si>
   <si>
+    <t>FR: 0.32
+V1: 135 V2: 1 Vties: 6</t>
+  </si>
+  <si>
     <t>FR: 0.25
 V1: 138 V2: 0 Vties: 4</t>
   </si>
@@ -367,10 +371,6 @@
 V1: 133 V2: 3 Vties: 6</t>
   </si>
   <si>
-    <t>FR: 0.32
-V1: 135 V2: 1 Vties: 6</t>
-  </si>
-  <si>
     <t>FR: 0.80
 V1: 34 V2: 15 Vties: 92</t>
   </si>
@@ -399,6 +399,10 @@
 V1: 36 V2: 7 Vties: 99</t>
   </si>
   <si>
+    <t>FR: 0.89
+V1: 58 V2: 12 Vties: 72</t>
+  </si>
+  <si>
     <t>FR: 0.78
 V1: 81 V2: 24 Vties: 11</t>
   </si>
@@ -407,10 +411,6 @@
 V1: 58 V2: 29 Vties: 55</t>
   </si>
   <si>
-    <t>FR: 0.89
-V1: 58 V2: 12 Vties: 72</t>
-  </si>
-  <si>
     <t>FR: 0.72
 V1: 86 V2: 35 Vties: 21</t>
   </si>
@@ -419,14 +419,14 @@
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>CR: 0.80
+V1: 129 V2: 2 Vties: 11</t>
+  </si>
+  <si>
     <t>CR: 0.45
 V1: 128 V2: 4 Vties: 3</t>
   </si>
   <si>
-    <t>CR: 0.80
-V1: 129 V2: 2 Vties: 11</t>
-  </si>
-  <si>
     <t>CR: 0.27
 V1: 136 V2: 3 Vties: 2</t>
   </si>
@@ -435,14 +435,14 @@
 V1: 41 V2: 10 Vties: 89</t>
   </si>
   <si>
+    <t>CR: 0.34
+V1: 81 V2: 19 Vties: 42</t>
+  </si>
+  <si>
     <t>CR: 0.41
 V1: 81 V2: 25 Vties: 7</t>
   </si>
   <si>
-    <t>CR: 0.34
-V1: 81 V2: 19 Vties: 42</t>
-  </si>
-  <si>
     <t>CR: 0.39
 V1: 95 V2: 34 Vties: 12</t>
   </si>
@@ -459,6 +459,10 @@
 V1: 39 V2: 21 Vties: 81</t>
   </si>
   <si>
+    <t>CR: 0.65
+V1: 92 V2: 16 Vties: 34</t>
+  </si>
+  <si>
     <t>CR: 0.37
 V1: 88 V2: 20 Vties: 12</t>
   </si>
@@ -467,14 +471,14 @@
 V1: 61 V2: 35 Vties: 46</t>
   </si>
   <si>
-    <t>CR: 0.65
-V1: 92 V2: 16 Vties: 34</t>
-  </si>
-  <si>
     <t>CR: 0.71
 V1: 90 V2: 1 Vties: 50</t>
   </si>
   <si>
+    <t>CR: 0.71
+V1: 135 V2: 1 Vties: 6</t>
+  </si>
+  <si>
     <t>CR: 0.78
 V1: 138 V2: 0 Vties: 4</t>
   </si>
@@ -483,10 +487,6 @@
 V1: 133 V2: 3 Vties: 6</t>
   </si>
   <si>
-    <t>CR: 0.71
-V1: 135 V2: 1 Vties: 6</t>
-  </si>
-  <si>
     <t>CR: 0.57
 V1: 34 V2: 15 Vties: 92</t>
   </si>
@@ -515,16 +515,16 @@
 V1: 36 V2: 7 Vties: 99</t>
   </si>
   <si>
+    <t>CR: 0.21
+V1: 58 V2: 12 Vties: 72</t>
+  </si>
+  <si>
     <t>CR: 0.25
 V1: 81 V2: 24 Vties: 11</t>
   </si>
   <si>
     <t>CR: 0.34
 V1: 58 V2: 29 Vties: 55</t>
-  </si>
-  <si>
-    <t>CR: 0.21
-V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
     <t>CR: 0.33
@@ -966,12 +966,6 @@
       <c r="E3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="I3" s="1" t="s">
         <v>41</v>
       </c>
@@ -980,14 +974,23 @@
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>42</v>
@@ -997,17 +1000,14 @@
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="D5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>33</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>43</v>
@@ -1130,12 +1130,6 @@
       <c r="E3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="I3" s="1" t="s">
         <v>70</v>
       </c>
@@ -1144,14 +1138,23 @@
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="D4" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>61</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>71</v>
@@ -1161,17 +1164,14 @@
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="D5" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>62</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>72</v>
@@ -1294,12 +1294,6 @@
       <c r="E3" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="I3" s="1" t="s">
         <v>99</v>
       </c>
@@ -1308,14 +1302,23 @@
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="D4" s="1" t="s">
         <v>86</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>100</v>
@@ -1325,17 +1328,14 @@
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="D5" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>91</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>101</v>
@@ -1458,12 +1458,6 @@
       <c r="E3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="I3" s="1" t="s">
         <v>128</v>
       </c>
@@ -1472,14 +1466,23 @@
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D4" s="1" t="s">
         <v>115</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>119</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>122</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>129</v>
@@ -1489,17 +1492,14 @@
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="D5" s="1" t="s">
         <v>116</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>120</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>130</v>

--- a/data/analysis_results/overview_aae.xlsx
+++ b/data/analysis_results/overview_aae.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="137">
   <si>
     <t>vs_Llama-2-7b-chat-hf</t>
   </si>
@@ -43,19 +43,22 @@
     <t>vs_gemini-1.5-flash</t>
   </si>
   <si>
+    <t>vs_gpt-4.1_errors</t>
+  </si>
+  <si>
     <t>Judge Model</t>
   </si>
   <si>
     <t>Mistral-7B-Instruct-v0.2</t>
   </si>
   <si>
+    <t>phi-4</t>
+  </si>
+  <si>
+    <t>Llama-3.3-70B-Instruct</t>
+  </si>
+  <si>
     <t>Qwen2.5-72B-Instruct</t>
-  </si>
-  <si>
-    <t>phi-4</t>
-  </si>
-  <si>
-    <t>Llama-3.3-70B-Instruct</t>
   </si>
   <si>
     <t>Qwen3-32B</t>
@@ -71,14 +74,14 @@
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>ASR: 0.57
+V1: 128 V2: 4 Vties: 3</t>
+  </si>
+  <si>
     <t>ASR: 0.20
 V1: 129 V2: 2 Vties: 11</t>
   </si>
   <si>
-    <t>ASR: 0.57
-V1: 128 V2: 4 Vties: 3</t>
-  </si>
-  <si>
     <t>ASR: 0.74
 V1: 136 V2: 3 Vties: 2</t>
   </si>
@@ -87,14 +90,14 @@
 V1: 41 V2: 10 Vties: 89</t>
   </si>
   <si>
+    <t>ASR: 0.78
+V1: 81 V2: 25 Vties: 7</t>
+  </si>
+  <si>
     <t>ASR: 0.81
 V1: 81 V2: 19 Vties: 42</t>
   </si>
   <si>
-    <t>ASR: 0.78
-V1: 81 V2: 25 Vties: 7</t>
-  </si>
-  <si>
     <t>ASR: 0.83
 V1: 95 V2: 34 Vties: 12</t>
   </si>
@@ -111,34 +114,34 @@
 V1: 39 V2: 21 Vties: 81</t>
   </si>
   <si>
+    <t>ASR: 0.77
+V1: 88 V2: 20 Vties: 12</t>
+  </si>
+  <si>
+    <t>ASR: 0.82
+V1: 61 V2: 35 Vties: 46</t>
+  </si>
+  <si>
     <t>ASR: 0.41
 V1: 92 V2: 16 Vties: 34</t>
   </si>
   <si>
-    <t>ASR: 0.77
-V1: 88 V2: 20 Vties: 12</t>
-  </si>
-  <si>
-    <t>ASR: 0.82
-V1: 61 V2: 35 Vties: 46</t>
-  </si>
-  <si>
     <t>ASR: 0.29
 V1: 90 V2: 1 Vties: 50</t>
   </si>
   <si>
+    <t>ASR: 0.22
+V1: 138 V2: 0 Vties: 4</t>
+  </si>
+  <si>
+    <t>ASR: 0.48
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
     <t>ASR: 0.30
 V1: 135 V2: 1 Vties: 6</t>
   </si>
   <si>
-    <t>ASR: 0.22
-V1: 138 V2: 0 Vties: 4</t>
-  </si>
-  <si>
-    <t>ASR: 0.48
-V1: 133 V2: 3 Vties: 6</t>
-  </si>
-  <si>
     <t>ASR: 0.62
 V1: 34 V2: 15 Vties: 92</t>
   </si>
@@ -167,35 +170,39 @@
 V1: 36 V2: 7 Vties: 99</t>
   </si>
   <si>
+    <t>ASR: 0.98
+V1: 81 V2: 24 Vties: 11</t>
+  </si>
+  <si>
+    <t>ASR: 0.98
+V1: 58 V2: 29 Vties: 55</t>
+  </si>
+  <si>
     <t>ASR: 0.95
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
-    <t>ASR: 0.98
-V1: 81 V2: 24 Vties: 11</t>
-  </si>
-  <si>
-    <t>ASR: 0.98
-V1: 58 V2: 29 Vties: 55</t>
-  </si>
-  <si>
     <t>ASR: 0.94
 V1: 86 V2: 35 Vties: 21</t>
   </si>
   <si>
+    <t>ASR: 0.29
+V1: 118 V2: 4 Vties: 20</t>
+  </si>
+  <si>
     <t>AASR: 0.00
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
     <t>AASR: 0.00
+V1: 128 V2: 4 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 129 V2: 2 Vties: 11</t>
   </si>
   <si>
     <t>AASR: 0.00
-V1: 128 V2: 4 Vties: 3</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 136 V2: 3 Vties: 2</t>
   </si>
   <si>
@@ -204,11 +211,11 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 81 V2: 25 Vties: 7</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 81 V2: 19 Vties: 42</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 81 V2: 25 Vties: 7</t>
   </si>
   <si>
     <t>AASR: 0.00
@@ -228,34 +235,34 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 88 V2: 20 Vties: 12</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 61 V2: 35 Vties: 46</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 92 V2: 16 Vties: 34</t>
   </si>
   <si>
     <t>AASR: 0.00
-V1: 88 V2: 20 Vties: 12</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 61 V2: 35 Vties: 46</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 90 V2: 1 Vties: 50</t>
   </si>
   <si>
     <t>AASR: 0.00
+V1: 138 V2: 0 Vties: 4</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 135 V2: 1 Vties: 6</t>
   </si>
   <si>
     <t>AASR: 0.00
-V1: 138 V2: 0 Vties: 4</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 133 V2: 3 Vties: 6</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 34 V2: 15 Vties: 92</t>
   </si>
   <si>
@@ -284,33 +291,37 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 81 V2: 24 Vties: 11</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 58 V2: 29 Vties: 55</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
     <t>AASR: 0.00
-V1: 81 V2: 24 Vties: 11</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 58 V2: 29 Vties: 55</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 86 V2: 35 Vties: 21</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 118 V2: 4 Vties: 20</t>
   </si>
   <si>
     <t>FR: 0.64
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>FR: 0.56
+V1: 128 V2: 4 Vties: 3</t>
+  </si>
+  <si>
     <t>FR: 0.26
 V1: 129 V2: 2 Vties: 11</t>
   </si>
   <si>
-    <t>FR: 0.56
-V1: 128 V2: 4 Vties: 3</t>
-  </si>
-  <si>
     <t>FR: 0.73
 V1: 136 V2: 3 Vties: 2</t>
   </si>
@@ -319,14 +330,14 @@
 V1: 41 V2: 10 Vties: 89</t>
   </si>
   <si>
+    <t>FR: 0.62
+V1: 81 V2: 25 Vties: 7</t>
+  </si>
+  <si>
     <t>FR: 0.76
 V1: 81 V2: 19 Vties: 42</t>
   </si>
   <si>
-    <t>FR: 0.62
-V1: 81 V2: 25 Vties: 7</t>
-  </si>
-  <si>
     <t>FR: 0.65
 V1: 95 V2: 34 Vties: 12</t>
   </si>
@@ -343,34 +354,34 @@
 V1: 39 V2: 21 Vties: 81</t>
   </si>
   <si>
+    <t>FR: 0.67
+V1: 88 V2: 20 Vties: 12</t>
+  </si>
+  <si>
+    <t>FR: 0.68
+V1: 61 V2: 35 Vties: 46</t>
+  </si>
+  <si>
     <t>FR: 0.51
 V1: 92 V2: 16 Vties: 34</t>
   </si>
   <si>
-    <t>FR: 0.67
-V1: 88 V2: 20 Vties: 12</t>
-  </si>
-  <si>
-    <t>FR: 0.68
-V1: 61 V2: 35 Vties: 46</t>
-  </si>
-  <si>
     <t>FR: 0.54
 V1: 90 V2: 1 Vties: 50</t>
   </si>
   <si>
+    <t>FR: 0.25
+V1: 138 V2: 0 Vties: 4</t>
+  </si>
+  <si>
+    <t>FR: 0.49
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
     <t>FR: 0.32
 V1: 135 V2: 1 Vties: 6</t>
   </si>
   <si>
-    <t>FR: 0.25
-V1: 138 V2: 0 Vties: 4</t>
-  </si>
-  <si>
-    <t>FR: 0.49
-V1: 133 V2: 3 Vties: 6</t>
-  </si>
-  <si>
     <t>FR: 0.80
 V1: 34 V2: 15 Vties: 92</t>
   </si>
@@ -399,34 +410,38 @@
 V1: 36 V2: 7 Vties: 99</t>
   </si>
   <si>
+    <t>FR: 0.78
+V1: 81 V2: 24 Vties: 11</t>
+  </si>
+  <si>
+    <t>FR: 0.79
+V1: 58 V2: 29 Vties: 55</t>
+  </si>
+  <si>
     <t>FR: 0.89
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
-    <t>FR: 0.78
-V1: 81 V2: 24 Vties: 11</t>
-  </si>
-  <si>
-    <t>FR: 0.79
-V1: 58 V2: 29 Vties: 55</t>
-  </si>
-  <si>
     <t>FR: 0.72
 V1: 86 V2: 35 Vties: 21</t>
   </si>
   <si>
+    <t>FR: 0.38
+V1: 118 V2: 4 Vties: 20</t>
+  </si>
+  <si>
     <t>CR: 0.81
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>CR: 0.45
+V1: 128 V2: 4 Vties: 3</t>
+  </si>
+  <si>
     <t>CR: 0.80
 V1: 129 V2: 2 Vties: 11</t>
   </si>
   <si>
-    <t>CR: 0.45
-V1: 128 V2: 4 Vties: 3</t>
-  </si>
-  <si>
     <t>CR: 0.27
 V1: 136 V2: 3 Vties: 2</t>
   </si>
@@ -435,14 +450,14 @@
 V1: 41 V2: 10 Vties: 89</t>
   </si>
   <si>
+    <t>CR: 0.41
+V1: 81 V2: 25 Vties: 7</t>
+  </si>
+  <si>
     <t>CR: 0.34
 V1: 81 V2: 19 Vties: 42</t>
   </si>
   <si>
-    <t>CR: 0.41
-V1: 81 V2: 25 Vties: 7</t>
-  </si>
-  <si>
     <t>CR: 0.39
 V1: 95 V2: 34 Vties: 12</t>
   </si>
@@ -459,34 +474,34 @@
 V1: 39 V2: 21 Vties: 81</t>
   </si>
   <si>
+    <t>CR: 0.37
+V1: 88 V2: 20 Vties: 12</t>
+  </si>
+  <si>
+    <t>CR: 0.48
+V1: 61 V2: 35 Vties: 46</t>
+  </si>
+  <si>
     <t>CR: 0.65
 V1: 92 V2: 16 Vties: 34</t>
   </si>
   <si>
-    <t>CR: 0.37
-V1: 88 V2: 20 Vties: 12</t>
-  </si>
-  <si>
-    <t>CR: 0.48
-V1: 61 V2: 35 Vties: 46</t>
-  </si>
-  <si>
     <t>CR: 0.71
 V1: 90 V2: 1 Vties: 50</t>
   </si>
   <si>
+    <t>CR: 0.78
+V1: 138 V2: 0 Vties: 4</t>
+  </si>
+  <si>
+    <t>CR: 0.53
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
     <t>CR: 0.71
 V1: 135 V2: 1 Vties: 6</t>
   </si>
   <si>
-    <t>CR: 0.78
-V1: 138 V2: 0 Vties: 4</t>
-  </si>
-  <si>
-    <t>CR: 0.53
-V1: 133 V2: 3 Vties: 6</t>
-  </si>
-  <si>
     <t>CR: 0.57
 V1: 34 V2: 15 Vties: 92</t>
   </si>
@@ -515,20 +530,24 @@
 V1: 36 V2: 7 Vties: 99</t>
   </si>
   <si>
+    <t>CR: 0.25
+V1: 81 V2: 24 Vties: 11</t>
+  </si>
+  <si>
+    <t>CR: 0.34
+V1: 58 V2: 29 Vties: 55</t>
+  </si>
+  <si>
     <t>CR: 0.21
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
-    <t>CR: 0.25
-V1: 81 V2: 24 Vties: 11</t>
-  </si>
-  <si>
-    <t>CR: 0.34
-V1: 58 V2: 29 Vties: 55</t>
-  </si>
-  <si>
     <t>CR: 0.33
 V1: 86 V2: 35 Vties: 21</t>
+  </si>
+  <si>
+    <t>CR: 0.72
+V1: 118 V2: 4 Vties: 20</t>
   </si>
 </sst>
 </file>
@@ -889,15 +908,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="10" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="11" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -923,127 +942,133 @@
       <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1053,15 +1078,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="10" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="11" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1087,127 +1112,133 @@
       <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="H7" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1217,15 +1248,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="10" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="11" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1251,127 +1282,133 @@
       <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="I6" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="H7" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1381,15 +1418,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="10" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="11" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1415,127 +1452,133 @@
       <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="I6" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="H7" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_results/overview_aae.xlsx
+++ b/data/analysis_results/overview_aae.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="145">
   <si>
     <t>vs_Llama-2-7b-chat-hf</t>
   </si>
@@ -186,8 +186,16 @@
 V1: 86 V2: 35 Vties: 21</t>
   </si>
   <si>
-    <t>ASR: 0.29
+    <t>ASR: 0.46
+V1: 125 V2: 4 Vties: 13</t>
+  </si>
+  <si>
+    <t>ASR: 0.34
 V1: 118 V2: 4 Vties: 20</t>
+  </si>
+  <si>
+    <t>ASR: 0.36
+V1: 135 V2: 2 Vties: 5</t>
   </si>
   <si>
     <t>AASR: 0.00
@@ -307,7 +315,15 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 125 V2: 4 Vties: 13</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 118 V2: 4 Vties: 20</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 135 V2: 2 Vties: 5</t>
   </si>
   <si>
     <t>FR: 0.64
@@ -426,8 +442,16 @@
 V1: 86 V2: 35 Vties: 21</t>
   </si>
   <si>
+    <t>FR: 0.49
+V1: 125 V2: 4 Vties: 13</t>
+  </si>
+  <si>
+    <t>FR: 0.42
+V1: 118 V2: 4 Vties: 20</t>
+  </si>
+  <si>
     <t>FR: 0.38
-V1: 118 V2: 4 Vties: 20</t>
+V1: 135 V2: 2 Vties: 5</t>
   </si>
   <si>
     <t>CR: 0.81
@@ -546,8 +570,16 @@
 V1: 86 V2: 35 Vties: 21</t>
   </si>
   <si>
-    <t>CR: 0.72
+    <t>CR: 0.56
+V1: 125 V2: 4 Vties: 13</t>
+  </si>
+  <si>
+    <t>CR: 0.67
 V1: 118 V2: 4 Vties: 20</t>
+  </si>
+  <si>
+    <t>CR: 0.64
+V1: 135 V2: 2 Vties: 5</t>
   </si>
 </sst>
 </file>
@@ -997,6 +1029,9 @@
       <c r="I3" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="J3" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
@@ -1015,7 +1050,7 @@
         <v>43</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1036,6 +1071,9 @@
       </c>
       <c r="I5" s="1" t="s">
         <v>44</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1121,25 +1159,25 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1147,25 +1185,28 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1173,19 +1214,19 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1193,19 +1234,22 @@
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1213,13 +1257,13 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1227,10 +1271,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1238,7 +1282,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1291,25 +1335,25 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1317,25 +1361,28 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1343,19 +1390,19 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1363,19 +1410,22 @@
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1383,13 +1433,13 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1397,10 +1447,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1408,7 +1458,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1461,25 +1511,25 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1487,25 +1537,28 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1513,19 +1566,19 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1533,19 +1586,22 @@
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1553,13 +1609,13 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1567,10 +1623,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1578,7 +1634,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_results/overview_aae.xlsx
+++ b/data/analysis_results/overview_aae.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="137">
   <si>
     <t>vs_Llama-2-7b-chat-hf</t>
   </si>
@@ -186,16 +186,8 @@
 V1: 86 V2: 35 Vties: 21</t>
   </si>
   <si>
-    <t>ASR: 0.46
-V1: 125 V2: 4 Vties: 13</t>
-  </si>
-  <si>
-    <t>ASR: 0.34
+    <t>ASR: 0.29
 V1: 118 V2: 4 Vties: 20</t>
-  </si>
-  <si>
-    <t>ASR: 0.36
-V1: 135 V2: 2 Vties: 5</t>
   </si>
   <si>
     <t>AASR: 0.00
@@ -315,15 +307,7 @@
   </si>
   <si>
     <t>AASR: 0.00
-V1: 125 V2: 4 Vties: 13</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 118 V2: 4 Vties: 20</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 135 V2: 2 Vties: 5</t>
   </si>
   <si>
     <t>FR: 0.64
@@ -442,16 +426,8 @@
 V1: 86 V2: 35 Vties: 21</t>
   </si>
   <si>
-    <t>FR: 0.49
-V1: 125 V2: 4 Vties: 13</t>
-  </si>
-  <si>
-    <t>FR: 0.42
+    <t>FR: 0.38
 V1: 118 V2: 4 Vties: 20</t>
-  </si>
-  <si>
-    <t>FR: 0.38
-V1: 135 V2: 2 Vties: 5</t>
   </si>
   <si>
     <t>CR: 0.81
@@ -570,16 +546,8 @@
 V1: 86 V2: 35 Vties: 21</t>
   </si>
   <si>
-    <t>CR: 0.56
-V1: 125 V2: 4 Vties: 13</t>
-  </si>
-  <si>
-    <t>CR: 0.67
+    <t>CR: 0.72
 V1: 118 V2: 4 Vties: 20</t>
-  </si>
-  <si>
-    <t>CR: 0.64
-V1: 135 V2: 2 Vties: 5</t>
   </si>
 </sst>
 </file>
@@ -1029,9 +997,6 @@
       <c r="I3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
@@ -1050,7 +1015,7 @@
         <v>43</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1071,9 +1036,6 @@
       </c>
       <c r="I5" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1159,25 +1121,25 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1185,28 +1147,25 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1214,19 +1173,19 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1234,22 +1193,19 @@
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1257,13 +1213,13 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1271,10 +1227,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1282,7 +1238,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1335,25 +1291,25 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="G2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1361,28 +1317,25 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="D3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="G3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1390,19 +1343,19 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="G4" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="J4" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1410,22 +1363,19 @@
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="D5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1433,13 +1383,13 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="I6" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1447,10 +1397,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1458,7 +1408,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1511,25 +1461,25 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="E2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1537,28 +1487,25 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="E3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1566,19 +1513,19 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1586,22 +1533,19 @@
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1609,13 +1553,13 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1623,10 +1567,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1634,7 +1578,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
